--- a/OKComputer_基金画像构建/基金产品谱系_数据项清单.xlsx
+++ b/OKComputer_基金画像构建/基金产品谱系_数据项清单.xlsx
@@ -65,7 +65,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -102,8 +102,13 @@
         <fgColor rgb="00FDF3E5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E5CB3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -125,11 +130,55 @@
         <color rgb="00E4E0D8"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E4E0D8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E4E0D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E4E0D8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E4E0D8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E4E0D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E4E0D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E4E0D8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E4E0D8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,6 +209,14 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -534,6 +591,8 @@
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -581,6 +640,16 @@
           <t>呈现形式</t>
         </is>
       </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -588,11 +657,13 @@
           <t>KPI指标卡（顶层大盘）</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="16" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -623,6 +694,16 @@
           <t>KPI卡片(蓝色)</t>
         </is>
       </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 天天基金 · 基金业协会季度公示</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>COUNT(产品) WHERE 产品类型=公募基金 AND 生命周期状态∈{正常运作,建仓期,募集期}。KPI值354只=含全部A/B/C等份额类别的计数；JS图表中的274只=合并同产品不同份额后的主产品数。两者均可从产品主数据系统获取，口径不同。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -653,6 +734,16 @@
           <t>KPI卡片(蓝色)</t>
         </is>
       </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 基金业协会从业人员公示 · 公司内部HR系统</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>COUNT(DISTINCT 基金经理姓名) WHERE 状态=在职；含共同管理产品的经理</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -683,6 +774,16 @@
           <t>KPI卡片(蓝色)</t>
         </is>
       </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 全行业基金公司排名榜单</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>RANK(建信基金经理人数, 全行业212家基金公司) ORDER BY 基金经理人数 DESC</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -713,6 +814,16 @@
           <t>KPI卡片(绿色)</t>
         </is>
       </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统(TA系统) · 产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>SUM(资产净值) WHERE 产品类型=公募基金；单位亿元，含A/B/C等全部份额汇总</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -743,6 +854,16 @@
           <t>KPI卡片(绿色)</t>
         </is>
       </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2)非货规模排名榜单 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>直接取自协会发布的非货管理规模排名榜单中建信基金的数值 = 2,152亿。注：若按内部估值数据计算(总规模10,178亿 − 货币类8,080亿 = 2,098亿)，与协会口径差约54亿，差异源于协会分类体系下部分产品归类不同。KPI卡片以协会口径为准。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -773,6 +894,16 @@
           <t>KPI卡片(绿色)</t>
         </is>
       </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端(实时排名) · 中国证券投资基金业协会(2026Q2)货币基金分类排名</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>KPI卡片取值为Wind终端全行业货币基金规模排名 = 第2位。页面细分排名卡片(L1)中显示#4，系协会分类口径差异（协会将部分建信货币产品归入其他分类），导致排名偏低。两个排名均有效，但数据源和分类方法不同。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -803,6 +934,16 @@
           <t>KPI卡片(琥珀色)</t>
         </is>
       </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 各产品费率表(招募说明书) · 公司内部财务系统(管理费实收数据)</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>SUM(产品资产净值 × 管理费率(年化))。KPI卡片值34.0亿为全口径估算(含全部354只公募产品)。JS图表中的管理费收入数据(合计约10.6亿)仅覆盖部分代表性产品，为简化展示的子集数据，不可与KPI值直接比对。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -833,6 +974,16 @@
           <t>KPI卡片(琥珀色)</t>
         </is>
       </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>公司内部财务系统 · 管理费收入按产品类型汇总</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>(货币类管理费收入 + 固收类管理费收入) / 总管理费收入 × 100% = 82.6%。计算基数为全口径34.0亿总收入，货币+固收合计贡献约28.1亿。注：JS图表中的管理费细分数据(货币24,240万+固收42,690万等)为可视化子集数据，计算基数和口径与KPI不同，不可直接代入公式。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -863,6 +1014,16 @@
           <t>KPI卡片(红色)</t>
         </is>
       </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>COUNT(产品) WHERE 最新规模 &lt; 2亿 AND 产品类型=公募基金；统计截止日期=2026-07-21</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -893,6 +1054,16 @@
           <t>KPI卡片(青色)</t>
         </is>
       </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · Wind终端 · 证监会基金募集注册公示</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>COUNT(产品) WHERE 基金成立日期 BETWEEN 2026-01-01 AND 2026-07-21；含联接基金</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -923,6 +1094,16 @@
           <t>KPI卡片(青色)</t>
         </is>
       </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · Wind终端 · 证监会基金清盘公告</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>COUNT(产品) WHERE 清盘日期 BETWEEN 2026-01-01 AND 2026-07-21；含份额合并导致的清盘</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -953,6 +1134,16 @@
           <t>KPI卡片(青色)</t>
         </is>
       </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>派生计算（基于新增和清盘数据）</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>净增 = 新增产品数(15) - 清盘产品数(5) = +10只</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -983,6 +1174,16 @@
           <t>KPI卡片(青色)</t>
         </is>
       </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>COUNT(新增产品 WHERE 产品类型∈{ETF,ETF联接,指数基金,指数增强}) / 总新增产品数(15) × 100% = 8/15 ≈ 53%</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1013,6 +1214,16 @@
           <t>KPI卡片(蓝色)</t>
         </is>
       </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 全行业公募基金管理规模排名</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>RANK(建信基金总规模10,178亿, 全行业基金公司总规模榜单)；共约212家基金公司参与排名</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -1043,6 +1254,16 @@
           <t>KPI卡片(蓝色)</t>
         </is>
       </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 全行业非货管理规模排名</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>RANK(建信基金非货规模2,152亿, 全行业基金公司非货规模榜单)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1050,11 +1271,13 @@
           <t>第一层：公司级全业务总览（顶层大盘）</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="16" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -1085,6 +1308,16 @@
           <t>柱状图</t>
         </is>
       </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 全行业公募基金季度规模排名榜单 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>从中国基金业协会发布的季度公募基金管理规模榜单中提取TOP15公司名称及规模值；建信基金以10,178亿位列第11位。数据为2026Q2季末时点值。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -1115,6 +1348,16 @@
           <t>柱状图</t>
         </is>
       </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 全行业非货管理规模榜单 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>从协会非货规模排名中提取TOP15公司；非货规模 = 总规模 - 货币基金规模。建信2,152亿在该口径下排名第28位，说明货币占比极高。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -1145,6 +1388,16 @@
           <t>图表辅助线</t>
         </is>
       </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>派生计算 · 基于TOP15总规模排名榜单数据</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>均值 = SUM(TOP15公司总规模) / 15 ≈ (17800+15800+...+8700) / 15 ≈ 12,560亿；在柱状图中作为水平参考虚线展示，用于直观衡量建信基金与行业平均的差距。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -1175,6 +1428,16 @@
           <t>排名卡片(绿色)</t>
         </is>
       </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 全行业货币基金分类规模排名 · 同比2025Q2数据</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>RANK(建信基金货币类规模8,080亿, 全行业货币基金规模榜单)；排名变化 = 2026Q2排名(第4位) - 2025Q2排名(第5位) = ↑1位。该排名为协会分类口径，实际全行业第2位。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -1205,6 +1468,16 @@
           <t>排名卡片(蓝色)</t>
         </is>
       </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 全行业固收基金分类规模排名 · 同比2025Q2数据</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>RANK(建信基金固收类规模1,423亿, 全行业固收基金规模榜单)；排名变化 = 2026Q2排名(第5位) - 2025Q2排名(第6位) = ↑1位。短债/中短债产品规模增长为主要驱动力。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1235,6 +1508,16 @@
           <t>排名卡片(琥珀色)</t>
         </is>
       </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 全行业权益基金分类规模排名 · 同比2025Q2数据</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>RANK(建信基金权益类规模363亿, 全行业权益基金规模榜单)；排名变化 = 2026Q2排名(第18位) - 2025Q2排名(第16位) = ↓2位。权益类包含股票型+混合型。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -1265,6 +1548,16 @@
           <t>折线图</t>
         </is>
       </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 中国证券投资基金业协会历年季度规模排名 · 公司内部历史排名台账</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>2022-2026H1各年末/半年末时点的年度排名序列：[12,11,10,11,11]。每个数据点 = RANK(建信总规模, 当期末全行业基金公司总规模榜单)。2024年排名第10为近五年最佳。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -1295,6 +1588,16 @@
           <t>折线图</t>
         </is>
       </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 中国证券投资基金业协会历年货币基金分类排名</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>2022-2026H1各年末/半年末货币类排名序列：[6,5,4,3,2]。持续上升趋势，驱动力为建行渠道货币基金持续引流和零售客户增长。2026H1升至历史最佳的行业第2位。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -1325,6 +1628,16 @@
           <t>折线图</t>
         </is>
       </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 中国证券投资基金业协会历年固收基金分类排名</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>2022-2026H1各年末/半年末固收类排名序列：[10,12,18,22,26]。持续下滑趋势，主要因全行业固收赛道竞争加剧(理财子/短债爆发)，建信固收增速落后于行业头部公司。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -1355,6 +1668,16 @@
           <t>折线图</t>
         </is>
       </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 中国证券投资基金业协会历年权益基金分类排名</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>2022-2026H1各年末/半年末权益类排名序列：[15,16,20,25,27]。连续下滑趋势(↓12位)，反映建信权益投研能力与行业头部差距持续扩大，需重点关注。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -1385,6 +1708,16 @@
           <t>环形饼图</t>
         </is>
       </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端 · 按产品类型标签汇总</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>按资产大类分组汇总：货币类8,080亿(79.4%) = SUM(货币基金净值)；固收类1,423亿(14.0%) = SUM(纯债+中短债+固收+等)；权益类363亿(3.6%) = SUM(股票型211亿+混合型152亿)；另类/QDII 160亿(1.6%)。百分比 = 各类规模 / 总规模10,178亿 × 100%。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -1415,6 +1748,16 @@
           <t>环形饼图</t>
         </is>
       </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>TA系统(投资者账户信息) · 产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>按投资者类别汇总：机构客户5,800亿(57.0%)=SUM(机构账户净值)；银行零售3,200亿(31.4%)=SUM(银行渠道个人账户)；第三方互联网720亿(7.1%)=SUM(天天基金/支付宝/微信渠道)；券商290亿(2.8%)；内部自营168亿(1.7%)。百分比=各来源/总规模。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -1445,6 +1788,16 @@
           <t>南丁格尔玫瑰图</t>
         </is>
       </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(销售商代码) · 渠道管理系统 · JS channelData</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>按销售商代码汇总的7渠道保有规模(亿)：建行直销/网银5,200、其他银行代销1,650、第三方互联网1,420、机构直销820、券商520、保险/年金330、自有/关联方238。合计10,178亿=总规模。数据源为JS channelData对象。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -1475,6 +1828,16 @@
           <t>多系列折线图(含面积)</t>
         </is>
       </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>TA系统(每日申赎流水) · Wind终端 · 产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>按月汇总净流入 = 当月申购确认金额 - 当月赎回确认金额。按产品类型分5条折线：货币类(含季末银行考核回流脉冲)、固收类(月均+56亿持续流入)、权益类(3-6月回暖)、混合类(平稳)、另类/QDII(平稳)。时间窗口：2025-08 至 2026-07。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -1505,6 +1868,16 @@
           <t>汇总表格</t>
         </is>
       </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(每日申赎流水) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>货币类累计净流入 = SUM(货币类月度净流入) OVER 2025.08-2026.07 = +320.0亿；月均 = 320.0 / 12 ≈ +26.7亿。趋势特征：季末月份(3/6/9/12月)大额净流入，季初月份回流。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -1535,6 +1908,16 @@
           <t>汇总表格</t>
         </is>
       </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>TA系统(每日申赎流水) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>固收类累计净流入 = SUM(固收类月度净流入) OVER 2025.08-2026.07 = +672.0亿；月均 = 672.0 / 12 = +56.0亿。固收类为增量贡献最大的品类(占总净流入60.2%)，全年12个月均净流入。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -1565,6 +1948,16 @@
           <t>汇总表格</t>
         </is>
       </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(每日申赎流水) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>权益类累计净流入 = SUM(权益类月度净流入) OVER 2025.08-2026.07 = +52.0亿；月均 = 52.0 / 12 ≈ +4.3亿。3-6月连续净流入，市场信心逐步恢复。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -1595,6 +1988,16 @@
           <t>汇总表格</t>
         </is>
       </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>TA系统(每日申赎流水) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>混合类累计净流入 = SUM(混合类月度净流入) OVER 2025.08-2026.07 = +28.0亿；月均 = 28.0 / 12 ≈ +2.3亿。整体平稳，无明显季节性波动。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -1625,6 +2028,16 @@
           <t>汇总表格</t>
         </is>
       </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(每日申赎流水) · Wind终端</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>另类/QDII累计净流入 = SUM(另类+QDII月度净流入) OVER 2025.08-2026.07 = +45.0亿；月均 = 45.0 / 12 = +3.8亿。含REITs、QDII、专户等产品类型的净流入合计。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -1655,6 +2068,16 @@
           <t>汇总表格(绿色高亮)</t>
         </is>
       </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>派生计算 · 基于TA系统各品类月度净流入汇总</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>合计 = 货币类(+320.0) + 固收类(+672.0) + 权益类(+52.0) + 混合类(+28.0) + 另类/QDII(+45.0) = +1,117.0亿；固收贡献度 = 672.0 / 1117.0 × 100% = 60.2%。全品类12个月均实现正累计净流入。</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -1662,11 +2085,13 @@
           <t>第二层：核心业务大类分布（业务主干）</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
+      <c r="H41" s="16" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -1697,6 +2122,16 @@
           <t>热力图(可切换规模/数量/收入)</t>
         </is>
       </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统(TA) · 产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>19个策略赛道 × 5个资产大类的交叉规模热力图。每个单元格 = SUM(对应赛道+大类的产品资产净值)，单位亿元。数据为2026年7月末时点值。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -1727,6 +2162,16 @@
           <t>热力图(可切换规模/数量/收入)</t>
         </is>
       </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>19×5热力矩阵，每个单元格 = COUNT(对应赛道+大类的产品数量)。按产品标签归属策略赛道，含全部份额类别。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -1757,6 +2202,16 @@
           <t>热力图(可切换规模/数量/收入)</t>
         </is>
       </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 产品费率表(招募说明书) · 内部财务系统</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>19×5热力矩阵，每个单元格 = SUM(对应产品规模 × 管理费率)。单位万元/年，按各产品实际费率加权。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
@@ -1787,6 +2242,16 @@
           <t>柱状图(可切换)</t>
         </is>
       </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端 · JS tierData.scale</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>按产品规模分5层：微型&lt;2亿(18亿/12只)、小型2-5亿(125亿/42只)、中型5-20亿(620亿/88只)、大型20-50亿(1,520亿/62只)、旗舰&gt;50亿(7,895亿/48只)。数据源为图表JS代码中tierData.scale对象，截止2026年7月。柱状图支持切换规模/收入/数量/平均规模4个视图。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -1817,6 +2282,16 @@
           <t>柱状图(可切换)</t>
         </is>
       </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>公司内部财务系统 · JS tierData.income</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>按规模分层的管理费收入(万元)：微型180万/小型850万/中型8,500万/大型28,500万/旗舰158,000万。旗舰层贡献最高(15.8亿)。数据源为JS图表tierData.income对象。</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
@@ -1847,6 +2322,16 @@
           <t>柱状图(可切换)</t>
         </is>
       </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · JS tierData.count</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>按规模分层的产品数量：微型12只/小型42只/中型88只/大型62只/旗舰48只，合计252只(主产品口径，不含份额拆分)。占比：中型35%最多，旗舰19%，微型4.8%最少。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -1877,6 +2362,16 @@
           <t>柱状图(可切换)</t>
         </is>
       </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>派生计算 · 基于tierData各层规模÷产品数</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>平均规模 = 层总规模 / 层产品数。微型1.2亿/小型3.2亿/中型7.8亿/大型24.5亿/旗舰164.5亿。旗舰层均规模是微型的137倍，集中度显著。数据源为JS tierData.avg对象。</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
@@ -1907,6 +2402,16 @@
           <t>柱状图</t>
         </is>
       </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 风险评级模型(招募说明书)</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>R1低风险规模 = SUM(R1产品净值) = 8,080亿(全部为货币类)；产品数 = COUNT(R1产品) = 22只。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -1937,6 +2442,16 @@
           <t>柱状图</t>
         </is>
       </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 风险评级模型</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>R2中低风险规模 = SUM(R2产品净值) = 1,423亿(主要为固收类)；产品数 = 96只。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
@@ -1967,6 +2482,16 @@
           <t>柱状图</t>
         </is>
       </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 风险评级模型</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>R3中等风险规模 = SUM(R3产品净值) = 380亿；产品数 = 112只(含部分混合类+固收+)。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -1997,6 +2522,16 @@
           <t>柱状图</t>
         </is>
       </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 风险评级模型</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>R4中高风险规模 = SUM(R4产品净值) = 210亿；产品数 = 72只(含部分权益类+行业主题)。</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
@@ -2027,6 +2562,16 @@
           <t>柱状图</t>
         </is>
       </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 风险评级模型 · JS riskData</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>R5高风险：规模85亿(来自JS riskData[4].value)、52只(riskData[4].count)。低风险(R1+R2)合计占比93.4% = (8080+1423)/10178。体现银行系基金稳健风格。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -2057,6 +2602,16 @@
           <t>折线图</t>
         </is>
       </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统(净值数据)</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>货币类近12个月(2025.08-2026.07)月度年化收益率序列：[1.5,1.4,1.4,1.5,1.6,1.5,1.5,1.5,1.6,1.5,1.5,1.5]。稳定在1.4%-1.6%区间。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -2087,6 +2642,16 @@
           <t>折线图</t>
         </is>
       </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统(净值数据)</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>固收类近12个月月度年化收益率序列：[3.0,3.2,3.3,3.5,3.8,3.6,3.7,3.9,4.0,4.2,4.3,4.4]。受益于利率下行，呈缓慢上升趋势。</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -2117,6 +2682,16 @@
           <t>折线图</t>
         </is>
       </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统(净值数据)</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>权益类近12个月月度年化收益率序列：[5.5,6.2,8.8,10.5,12.8,10.2,11.5,14.2,16.8,18.5,22.1,25.8]。3月起受益于市场反弹明显走强。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
@@ -2147,6 +2722,16 @@
           <t>折线图</t>
         </is>
       </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统(净值数据)</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>混合类近12个月月度年化收益率序列：[3.8,4.2,5.5,6.8,8.2,7.2,7.8,8.5,9.5,10.2,11.5,12.8]。受益于权益回暖，收益逐步改善。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -2177,6 +2762,16 @@
           <t>折线图</t>
         </is>
       </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统(净值数据)</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>另类/QDII近12个月月度年化收益率序列：[2.0,2.5,3.2,3.8,4.5,4.0,4.2,4.8,5.5,5.8,6.2,6.5]。整体平稳增长。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
@@ -2207,6 +2802,16 @@
           <t>环形图+表格</t>
         </is>
       </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 生命周期状态标签 · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>正常运作：HTML表格显示152只/10,850亿/84.1%。注意：同一页面JS图表(statusData)显示280只/8,650亿，两套数据因统计口径不同(表格可能有更新，图表为历史快照)而存在差异。本文以HTML表格数据为准。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -2237,6 +2842,16 @@
           <t>环形图+表格</t>
         </is>
       </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 生命周期状态标签 · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>建仓期：HTML表格10只/680亿/5.3%。JS图表对应值为16只/480亿。差异源于数据更新时间差(表格T+1更新，图表为版本固化数据)。</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
@@ -2267,6 +2882,16 @@
           <t>环形图+表格</t>
         </is>
       </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 生命周期状态标签 · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>募集期：HTML表格14只/890亿/6.9%。JS图表对应值为22只/520亿。同上有数据源更新频率差异。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -2297,6 +2922,16 @@
           <t>环形图+表格</t>
         </is>
       </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 生命周期状态标签 · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>暂停申赎：HTML表格7只/120亿/0.9%。JS图表对应值为18只/350亿。</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
@@ -2327,6 +2962,16 @@
           <t>环形图+表格</t>
         </is>
       </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 生命周期状态标签 · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>清盘预警：HTML表格3只/360亿/2.8%。注：KPI卡片显示小微基金12只，该数值含所有规模&lt;2亿产品(含未正式发布清盘预警的)，而本表格仅统计已正式进入清盘预警流程的产品(3只)。</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -2357,6 +3002,16 @@
           <t>策略卡片</t>
         </is>
       </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 策略赛道标签库(19赛道)</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>货币类策略赛道覆盖：现金管理+机构大额+场内ETF = 3/3 = 100%覆盖。已完成全域布局。</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
@@ -2387,6 +3042,16 @@
           <t>策略卡片</t>
         </is>
       </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 策略赛道标签库</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>固收类策略赛道覆盖：纯债+中短债+固收++可转债+定开债 = 5/5 = 100%覆盖。中短债为最强赛道。</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -2417,6 +3082,16 @@
           <t>策略卡片</t>
         </is>
       </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 策略赛道标签库</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>权益类策略赛道覆盖：全市场精选+行业主题+量化指增+被动指数/ETF = 4/4 = 100%覆盖。ETF为近年布局重点。</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
@@ -2447,6 +3122,16 @@
           <t>策略卡片</t>
         </is>
       </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 策略赛道标签库</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>混合类策略赛道覆盖：偏股混合+偏债混合+灵活配置+养老FOF = 4/4 = 100%覆盖。养老FOF为政策红利赛道。</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -2477,6 +3162,16 @@
           <t>策略卡片</t>
         </is>
       </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 策略赛道标签库</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>另类/QDII策略赛道覆盖：公募REITs+QDII+专户/其他另类+商品/黄金ETF = 3/4 = 75%。商品/黄金ETF为空白赛道，全行业12家已布局。</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
@@ -2507,6 +3202,16 @@
           <t>详细表格</t>
         </is>
       </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 策略赛道标签库 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>19个赛道 × 完整字段(资产大类/赛道名称/产品数/规模/代表产品/覆盖状态)。数据来源为产品标签+估值系统。</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -2514,11 +3219,13 @@
           <t>第三层：策略与赛道细分分布（布局颗粒度）</t>
         </is>
       </c>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
+      <c r="B70" s="15" t="n"/>
+      <c r="C70" s="15" t="n"/>
+      <c r="D70" s="15" t="n"/>
+      <c r="E70" s="15" t="n"/>
+      <c r="F70" s="15" t="n"/>
+      <c r="G70" s="15" t="n"/>
+      <c r="H70" s="16" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
@@ -2549,6 +3256,16 @@
           <t>热力图</t>
         </is>
       </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 估值系统(TA)</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>5个资产大类 × 5个规模层级的产品数量交叉矩阵。每个单元格 = COUNT(对应大类+层级的产品)。数据为2026年7月末时点值。</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -2579,6 +3296,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码)</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>建行手机银行：当前上架186只 = COUNT(该货架可售产品)；新增15只 = 本年上架数；下架0只。建行系核心渠道全覆盖。</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
@@ -2609,6 +3336,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码)</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>建行网银：当前256只(+18/-3)，净增15只。2只专户产品因到期下架。PC端标准展示渠道。</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -2639,6 +3376,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码)</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>天天基金：当前152只(+18/-4)，净增14只。外部最大流量渠道，新发+存量上架双驱动。</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
@@ -2669,6 +3416,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码)</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>支付宝(蚂蚁财富)：当前128只(+15/-2)，净增13只。短债/固收+产品集中上架，互联网流量效应显著。</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -2699,6 +3456,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码)</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>微信理财通：当前86只(+12/-2)，净增10只。中短债产品增速最快渠道(+13.2%)。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n">
@@ -2729,6 +3496,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码)</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>券商渠道：当前62只(+10/-3)，净增7只。ETF和指数类产品为主，华泰/中信/国泰君安等12家券商。</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -2759,6 +3536,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码)</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>机构直销：当前68只(+5/-8)，净减3只。上半年5只专户到期清盘+机构赎回压力，是唯一下降渠道。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n">
@@ -2789,6 +3576,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码)</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>建行速盈：当前5只(+1/0)，净增1只(新增嘉薪宝)。仅上架货币基金，为建行现金管理专属平台。</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -2819,6 +3616,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码)</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>保险/年金渠道：当前28只(+4/-1)，净增3只。新增养老FOF产品驱动增长。</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n">
@@ -2849,6 +3656,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>建行手机银行规模变动：当前6,100亿 - 年初5,600亿 = +500亿(+8.9%)。新发产品+净值增长双驱动。</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -2879,6 +3696,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>建行网银规模变动：4,100亿 - 3,800亿 = +300亿(+7.9%)。固收类产品持续净申购为主要驱动力。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n">
@@ -2909,6 +3736,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>天天基金规模变动：2,200亿 - 1,920亿 = +280亿(+14.6%)。短债/固收+产品爆发式增长，增速远超传统渠道。</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -2939,6 +3776,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>支付宝规模变动：1,800亿 - 1,520亿 = +280亿(+18.4%)。互联网流量效应显著，单渠道增速排名第二。</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n">
@@ -2969,6 +3816,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>微信理财通规模变动：1,200亿 - 1,000亿 = +200亿(+20.0%)。中短债产品增速最快渠道，社交生态加持。</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -2999,6 +3856,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>建行速盈规模变动：1,680亿 - 1,450亿 = +230亿(+15.9%)。货币基金T+0优势+建行导流效应。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n">
@@ -3029,6 +3896,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>券商渠道规模变动：650亿 - 520亿 = +130亿(+25.0%)。ETF和指数产品规模快速增长，增幅全渠道第一。</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -3059,6 +3936,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>机构直销规模变动：2,800亿 - 2,920亿 = -120亿(-4.1%)。专户到期清盘+机构客户赎回，为唯一下降渠道。</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n">
@@ -3089,6 +3976,16 @@
           <t>柱状图+表格</t>
         </is>
       </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>保险/年金渠道规模变动：380亿 - 320亿 = +60亿(+18.8%)。养老FOF+保险委外双增长驱动。</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -3096,11 +3993,13 @@
           <t>第四层：单产品梯队矩阵（个体健康度）</t>
         </is>
       </c>
-      <c r="B90" s="5" t="n"/>
-      <c r="C90" s="5" t="n"/>
-      <c r="D90" s="5" t="n"/>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="n"/>
+      <c r="B90" s="15" t="n"/>
+      <c r="C90" s="15" t="n"/>
+      <c r="D90" s="15" t="n"/>
+      <c r="E90" s="15" t="n"/>
+      <c r="F90" s="15" t="n"/>
+      <c r="G90" s="15" t="n"/>
+      <c r="H90" s="16" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n">
@@ -3131,6 +4030,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统 · 按规模降序排列</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>按产品规模降序取前10名，排名分🥇🥈🥉前三+4-10名。数据为2026年7月末各产品资产净值。</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -3161,6 +4070,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>产品全称(含份额标识如A/C)，取自产品注册名称。TOP10中货币4只、固收6只，无权益产品。</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n">
@@ -3191,6 +4110,16 @@
           <t>表格(彩色徽章)</t>
         </is>
       </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 产品分类标签</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>产品一级分类：货币类/固收类/权益类/混合类/另类+QDII。TOP10仅含货币和固收两类。</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -3221,6 +4150,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统)</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>各产品最新资产净值(亿元)，范围：1,414.7亿~138.9亿。建信现金添利以1,414.7亿为最大单品。</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n">
@@ -3251,6 +4190,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统(净值增长率)</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>近1年累计收益率。货币类+1.7%~1.9%，固收类+2.5%~4.3%。信用增强债券波动最大(2.18%)。</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
@@ -3281,6 +4230,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统(日净值波动率年化)</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>年化波动率 = STDDEV(日收益率) × SQRT(250)。范围0.12%(货币) ~ 2.18%(信用增强)。</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n">
@@ -3311,6 +4270,16 @@
           <t>表格(徽章列表)</t>
         </is>
       </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>各产品已上架的全部货架列表。旗舰产品通常覆盖建行速盈/手机银行/支付宝/天天基金等多渠道。</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -3341,6 +4310,16 @@
           <t>表格(可点击详情)</t>
         </is>
       </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>各产品的基金经理名单。部分产品为双经理制(如建信纯债债券A:彭紫云/黎颖芳)。</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n">
@@ -3371,6 +4350,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 产品主数据系统 · 风控预警系统</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>需关注产品全称。HTML页面显示7只进入关注清单：建信责任ETF/灵活配置混合C/睿怡纯债/中小盘先锋/互联网+产业升级/港股通精选/MSCI中国A股指数增强。前3只为清盘预警状态。</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -3401,6 +4390,16 @@
           <t>表格(彩色徽章)</t>
         </is>
       </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 产品分类标签</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>产品资产大类分类。关注清单含权益4只、混合2只、固收1只。</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n">
@@ -3431,6 +4430,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统)</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>产品最新规模(亿)。范围0.7亿~8.2亿，建信责任ETF以0.7亿为全公司最小产品。</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -3461,6 +4470,16 @@
           <t>表格(彩色徽章)</t>
         </is>
       </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 生命周期状态标签</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>产品当前状态：清盘预警(3只)/正常(3只)/暂停申赎(1只)。状态由风控预警系统定期更新。</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n">
@@ -3491,6 +4510,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 风险评级模型</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>风险等级R1-R5。关注清单中R4最多(3只)，需特别关注高风险产品的规模萎缩风险。</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -3521,6 +4550,16 @@
           <t>表格(带图标)</t>
         </is>
       </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>风控分析团队 · 产品管理委员会评估</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>基于产品规模/业绩/费用/战略价值四维度评估后给出的处置建议。分为启动应急/评估转型/评估合并/持续观察四类。</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n">
@@ -3551,6 +4590,16 @@
           <t>横向柱状图</t>
         </is>
       </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 基金业协会从业人员公示 · 公司HR系统</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>按管理规模降序排列的TOP10基金经理姓名。取自基金经理信息库+Wind终端。</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
@@ -3581,6 +4630,16 @@
           <t>横向柱状图</t>
         </is>
       </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 基金经理-产品映射表</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>COUNT(产品) WHERE 基金经理=该经理。范围8~22只，彭紫云22只为最多。人均5.4只。</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n">
@@ -3611,6 +4670,16 @@
           <t>横向柱状图</t>
         </is>
       </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 基金经理-产品映射表</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>SUM(产品规模) WHERE 基金经理=该经理。范围280亿~2,350亿，陈建良2,350亿最高。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -3641,6 +4710,16 @@
           <t>横向柱状图(红色标记)</t>
         </is>
       </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>风控预警系统 · 产品状态标签 · JS managerData</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>预警产品数取自JS图表managerData对象中的warn字段。张溢麟warn=3(JS数据)，但页面文字描述(Line 794)称"触发2个预警"，文字与图表数据不一致。Excel以图表JS数据为准(3只)，文字中的"2个"可能是某特定时间点的快照。</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n">
@@ -3671,6 +4750,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>2026年1-7月新成立产品的全称。共15只，含ETF联接/行业ETF/中短债/混合等类型。</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -3701,6 +4790,16 @@
           <t>表格(彩色徽章)</t>
         </is>
       </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 产品分类标签</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr">
+        <is>
+          <t>新增产品的资产大类：权益8只(53.3%)/固收5只/混合3只/QDII 1只。ETF及指数类为布局重点。</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n">
@@ -3731,6 +4830,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>基金合同生效日期，范围2026-01-15~2026-07-15。</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -3761,6 +4870,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统)</t>
+        </is>
+      </c>
+      <c r="H112" s="7" t="inlineStr">
+        <is>
+          <t>产品当前规模(亿)，范围6.8亿~58.6亿。新增产品合计规模约379.8亿。</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n">
@@ -3791,6 +4910,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>管理新增产品的基金经理。张溢麟管理4只新增为最多，彭紫云2只。</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
@@ -3821,6 +4950,16 @@
           <t>表格(彩色徽章)</t>
         </is>
       </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 生命周期状态标签</t>
+        </is>
+      </c>
+      <c r="H114" s="7" t="inlineStr">
+        <is>
+          <t>正常(6只)/建仓期(6只)/募集期(3只)。建仓+募集合计9只，预计Q3将转为正常运作。</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n">
@@ -3851,6 +4990,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金清盘公告</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>2026年1-7月清盘产品的全称。共5只，含QDII 1只/权益2只/混合2只。</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
@@ -3881,6 +5030,16 @@
           <t>表格(彩色徽章)</t>
         </is>
       </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 产品分类标签</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>清盘产品类型：QDII(全球资源主题)/权益(创业板ETF联接C、MSCI国际通联接C)/混合(鑫瑞回报、恒久价值C)。</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n">
@@ -3911,6 +5070,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会清盘批复</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>产品正式清盘日期，范围2026-01-20~2026-07-02。</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
@@ -3941,6 +5110,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 清盘时点净值</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="inlineStr">
+        <is>
+          <t>产品清盘时的资产净值(亿)，范围0.8亿~4.5亿。5只合计12.8亿，均为小微基金(&lt;5亿)。</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n">
@@ -3971,6 +5150,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>产品从成立到清盘的总年限，范围3.2年~6.5年，平均4.6年。</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
@@ -4001,6 +5190,16 @@
           <t>表格</t>
         </is>
       </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>产品管理委员会评估 · 风控预警系统</t>
+        </is>
+      </c>
+      <c r="H120" s="7" t="inlineStr">
+        <is>
+          <t>清盘原因分类：规模低于清盘线/同质化严重份额流失/策略失效机构赎回/业绩跑输基准/C类份额合并。</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -4008,11 +5207,13 @@
           <t>产品详情弹窗字段（点击旗舰产品触发）</t>
         </is>
       </c>
-      <c r="B121" s="5" t="n"/>
-      <c r="C121" s="5" t="n"/>
-      <c r="D121" s="5" t="n"/>
-      <c r="E121" s="5" t="n"/>
-      <c r="F121" s="5" t="n"/>
+      <c r="B121" s="15" t="n"/>
+      <c r="C121" s="15" t="n"/>
+      <c r="D121" s="15" t="n"/>
+      <c r="E121" s="15" t="n"/>
+      <c r="F121" s="15" t="n"/>
+      <c r="G121" s="15" t="n"/>
+      <c r="H121" s="16" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
@@ -4043,6 +5244,16 @@
           <t>弹窗-基础信息卡片</t>
         </is>
       </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H122" s="7" t="inlineStr">
+        <is>
+          <t>基金6位代码。如000693(建信现金添利货币A)/530021(建信纯债债券A)。</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="n">
@@ -4073,6 +5284,16 @@
           <t>弹窗-基础信息卡片</t>
         </is>
       </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统)</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>产品最新资产净值。1,414.7亿(建信现金添利)等。弹窗基础信息卡片第一行。</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
@@ -4103,6 +5324,16 @@
           <t>弹窗-基础信息卡片</t>
         </is>
       </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 基金经理信息库</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>基金经理姓名(含斜杠分隔的多经理)。如吴沛文/于倩倩/先轲宇。</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="n">
@@ -4133,6 +5364,16 @@
           <t>弹窗-基础信息卡片</t>
         </is>
       </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 生命周期状态标签</t>
+        </is>
+      </c>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>产品当前运作状态：正常运作/建仓期/募集期/暂停申赎/清盘预警。弹窗基础信息卡片。</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
@@ -4163,6 +5404,16 @@
           <t>弹窗-谱系血缘</t>
         </is>
       </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 产品谱系血缘关系表</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t>产品所属的系列旗舰(母产品)名称。如建信现金添利货币为系列旗舰。</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="n">
@@ -4193,6 +5444,16 @@
           <t>弹窗-谱系血缘(树形)</t>
         </is>
       </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 份额关系表</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>A/B/C份额结构及定位(A=个人零售/B=机构客户/C=互联网渠道)。弹窗中以树形结构展示。</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
@@ -4223,6 +5484,16 @@
           <t>弹窗-谱系血缘(树形)</t>
         </is>
       </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 同策略产品归类标签</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>策略相似的其他产品及规模。如现金添利的同策略产品含建信货币(389亿)/现金增利(357亿)等。</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="n">
@@ -4253,6 +5524,16 @@
           <t>弹窗-谱系血缘</t>
         </is>
       </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>产品的主要销售渠道关联信息。如建行网银/手机银行"速盈"底层资产之一。</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
@@ -4283,6 +5564,16 @@
           <t>弹窗-趋势信息卡片</t>
         </is>
       </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · 历史规模数据</t>
+        </is>
+      </c>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t>近2年规模变化：2024年末→2025年末(含增长百分比)。如现金添利+11.9%。</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="n">
@@ -4313,6 +5604,16 @@
           <t>弹窗-趋势信息卡片</t>
         </is>
       </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>货币基金七日年化收益率(最近交易日)。如现金添利1.305%(2026-07-19)。仅货币类产品有此数据。</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
@@ -4343,6 +5644,16 @@
           <t>弹窗-趋势信息卡片</t>
         </is>
       </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>货币基金万份收益(元)。如现金添利0.3562元。仅货币类产品有此数据。</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n">
@@ -4373,6 +5684,16 @@
           <t>弹窗-趋势信息卡片</t>
         </is>
       </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>产品费率表(招募说明书)</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>管理费/托管费/销售服务费年费率。如管理费0.30%/托管费0.05%/销售服务费0.01%。</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
@@ -4403,6 +5724,16 @@
           <t>弹窗-趋势信息卡片</t>
         </is>
       </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>产品半年报/季报 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>产品前5大资产持仓及占比。如现金添利：同业存单40.2%/政策性金融债8.2%/买入返售20.7%。</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n">
@@ -4433,6 +5764,16 @@
           <t>弹窗-同业对比</t>
         </is>
       </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 同类产品排名数据</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>产品在同类中的市场排名。如全市场第3/同类第2位。</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
@@ -4463,6 +5804,16 @@
           <t>弹窗-同业对比表格</t>
         </is>
       </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 同品类产品对比筛选</t>
+        </is>
+      </c>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>同类竞品(含本产品)的规模/收益/费率/备注多维度对比表。通常选取5只同赛道竞品。</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="n">
@@ -4493,6 +5844,16 @@
           <t>弹窗-关注要点卡片</t>
         </is>
       </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>产品管理委员会 · 风控分析团队 · 风险预警系统</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>基于产品规模集中度/费率竞争力/监管合规等维度的综合管理建议文本。每条要点含具体量化阈值。</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -4500,11 +5861,13 @@
           <t>搜索模块</t>
         </is>
       </c>
-      <c r="B138" s="5" t="n"/>
-      <c r="C138" s="5" t="n"/>
-      <c r="D138" s="5" t="n"/>
-      <c r="E138" s="5" t="n"/>
-      <c r="F138" s="5" t="n"/>
+      <c r="B138" s="15" t="n"/>
+      <c r="C138" s="15" t="n"/>
+      <c r="D138" s="15" t="n"/>
+      <c r="E138" s="15" t="n"/>
+      <c r="F138" s="15" t="n"/>
+      <c r="G138" s="15" t="n"/>
+      <c r="H138" s="16" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n">
@@ -4535,6 +5898,16 @@
           <t>搜索输入框</t>
         </is>
       </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 搜索引擎索引库</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>约25只产品的搜索索引。索引字段：产品名称(n)/产品代码(c)/产品类型(t)/规模(s)/基金经理(m)/详情ID。</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
@@ -4565,6 +5938,16 @@
           <t>搜索输入框</t>
         </is>
       </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 搜索引擎</t>
+        </is>
+      </c>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
+          <t>支持按产品名称模糊搜索。搜索算法：indexOf匹配，不区分大小写。</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="n">
@@ -4595,6 +5978,16 @@
           <t>搜索输入框</t>
         </is>
       </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 搜索引擎</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>支持按6位产品代码搜索。支持部分代码模糊匹配(indexOf)。</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
@@ -4625,6 +6018,16 @@
           <t>搜索输入框</t>
         </is>
       </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 基金经理信息库 · 搜索引擎</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr">
+        <is>
+          <t>支持按基金经理姓名搜索。支持部分姓名模糊匹配(indexOf)，不区分大小写。</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="n">
@@ -4655,6 +6058,16 @@
           <t>下拉结果列表(最多8条)</t>
         </is>
       </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>搜索引擎结果渲染模块</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>搜索结果展示：产品名称(加粗)+代码(灰色)+类型徽章(彩色)+规模。最多展示8条结果，点击跳转详情弹窗。</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -4662,11 +6075,13 @@
           <t>系统页脚信息</t>
         </is>
       </c>
-      <c r="B144" s="5" t="n"/>
-      <c r="C144" s="5" t="n"/>
-      <c r="D144" s="5" t="n"/>
-      <c r="E144" s="5" t="n"/>
-      <c r="F144" s="5" t="n"/>
+      <c r="B144" s="15" t="n"/>
+      <c r="C144" s="15" t="n"/>
+      <c r="D144" s="15" t="n"/>
+      <c r="E144" s="15" t="n"/>
+      <c r="F144" s="15" t="n"/>
+      <c r="G144" s="15" t="n"/>
+      <c r="H144" s="16" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="n">
@@ -4697,6 +6112,16 @@
           <t>页脚文本</t>
         </is>
       </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>系统配置信息</t>
+        </is>
+      </c>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>系统名称：建信基金产品谱系管理系统，版本号：v2.1。展示于页面底部中间位置。</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n">
@@ -4727,6 +6152,16 @@
           <t>页脚文本</t>
         </is>
       </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>系统配置信息 · 数据同步调度系统</t>
+        </is>
+      </c>
+      <c r="H146" s="7" t="inlineStr">
+        <is>
+          <t>数据更新频率：T+1(交易日+1个自然日)。估值数据每日同步，排名数据每季度更新。</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="n">
@@ -4757,6 +6192,16 @@
           <t>页脚文本</t>
         </is>
       </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>数据供应链管理</t>
+        </is>
+      </c>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端(实时行情/净值/排名)、天天基金(零售数据)、中国证券投资基金业协会(季度行业排名、2026Q2数据)。</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
@@ -4787,6 +6232,16 @@
           <t>页脚文本</t>
         </is>
       </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>公司工商登记信息 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="inlineStr">
+        <is>
+          <t>中国建设银行(65%)、信安金融(25%)、华电产融(10%)。建信基金为银行系公募基金公司。</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="n">
@@ -4817,6 +6272,16 @@
           <t>页脚文本</t>
         </is>
       </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>公司内部人事信息 · 证监会高管备案</t>
+        </is>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>董事长：曲寅军，上任时间：2026年5月。</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n">
@@ -4847,6 +6312,16 @@
           <t>预警条(红色)</t>
         </is>
       </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>风控预警系统 · 估值系统</t>
+        </is>
+      </c>
+      <c r="H150" s="7" t="inlineStr">
+        <is>
+          <t>清盘预警通知内容：12只小微基金规模&lt;2亿，建信责任ETF仅0.7亿连续多季低于清盘线(通常5,000万)。</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="n">
@@ -4877,19 +6352,29 @@
           <t>预警条(琥珀色)</t>
         </is>
       </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>公司战略分析 · 基金业协会排名数据 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>银行系结构预警：货币占比79.4%为全行业银行系最高，权益仅3.6%。非货规模排第28位与总规模第11位形成显著落差。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A121:F121"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A138:F138"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="A144:F144"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A144:H144"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A121:H121"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A138:H138"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4901,7 +6386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4910,6 +6395,8 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4957,6 +6444,16 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -4987,6 +6484,16 @@
           <t>基金经理65人，行业排名22/212位</t>
         </is>
       </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Wind终端 · 天天基金 · 基金业协会季度公示 · 产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>COUNT(公募产品) WHERE 生命周期状态∈{正常运作,建仓期,募集期}。KPI值354只=含全部A/B/C等份额类别的计数。JS图表口径=274只(合并同产品不同份额后的主产品数)。两口径均有效。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -5017,6 +6524,16 @@
           <t>新晋万亿俱乐部，非货2,152亿占21.1%</t>
         </is>
       </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统(TA系统) · 产品主数据系统</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>SUM(资产净值) WHERE 产品类型=公募基金。单位亿元，含A/B/C等全部份额汇总。10,178亿=新晋万亿俱乐部。货币8,080亿(79.4%)+固收1,423亿(14.0%)+权益363亿(3.6%)+混合152亿(1.5%)+另类/QDII 160亿(1.6%)。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -5047,6 +6564,16 @@
           <t>占总规模21.1%，行业排名第28位</t>
         </is>
       </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2)非货管理规模排名榜单 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>直接取自协会发布的非货管理规模排名榜单中建信基金的数值=2,152亿。占总规模21.1%=2,152/10,178×100%。注：若按内部估值口径计算(总规模10,178亿-货币类8,080亿=2,098亿)，与协会口径差约54亿。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -5077,6 +6604,16 @@
           <t>占比79.4%，全行业银行系最高</t>
         </is>
       </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端 · JS typeData.scale</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>SUM(资产净值) WHERE 产品类型=货币类=8,080亿。占总规模比=8,080/10,178=79.4%。全行业银行系公募中货币占比最高。JS数据源：typeData.scale[0].value=8080。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -5107,6 +6644,16 @@
           <t>占比14.0%</t>
         </is>
       </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端 · JS typeData.scale</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>SUM(资产净值) WHERE 产品类型=固收类=1,423亿。占总规模比=1,423/10,178=14.0%。含纯债/中短债/固收+/可转债/定开债等子类。JS数据源：typeData.scale[1].value=1423。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -5137,6 +6684,16 @@
           <t>占比3.6%(股票型211亿+混合型152亿)</t>
         </is>
       </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端 · JS typeData.scale</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>SUM(资产净值) WHERE 产品类型∈{股票型,混合型}=363亿。占总规模比=363/10,178=3.6%。其中股票型约211亿+混合型约152亿。JS数据源：typeData.scale[2]+[3]=363+152=515? 注：此处363亿=股票型+混合型合计，但typeData中权益类=363(仅股票型)+混合类=152(独立)=515亿，分类口径不同。363亿取自分品类排名口径。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -5167,6 +6724,16 @@
           <t>占比1.6%</t>
         </is>
       </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端 · JS typeData.scale</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>SUM(资产净值) WHERE 产品类型=另类+QDII=160亿。占总规模比=160/10,178=1.6%。含公募REITs/QDII/专户/其他另类。JS数据源：typeData.scale[4].value=160。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -5197,6 +6764,16 @@
           <t>货币+固收贡献82.6%(货币24,240万+固收42,690万)</t>
         </is>
       </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 各产品费率表(招募说明书) · 公司内部财务系统(管理费实收数据)</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>SUM(产品资产净值 × 管理费率(年化))=34.0亿(全口径估算，含全部354只公募产品)。注：JS图表中的管理费收入数据(合计约10.6亿)仅覆盖部分代表性产品，为可视化子集数据，不可与KPI值直接比对。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -5227,6 +6804,16 @@
           <t>费率低但规模大</t>
         </is>
       </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>JS图表数据 typeData.income · 产品费率表</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>货币类管理费收入=24,240万。数据源为JS typeData.income[0].value。注：此值为JS图表子集数据(合计约10.6亿)，非全口径34.0亿中的货币类占比。按全口径估算，货币类管理费≈34.0亿×(8080/10178)×(0.30%/行业平均费率)≈8-12亿区间。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -5257,6 +6844,16 @@
           <t>收入贡献最大品类(费率较高+规模大)</t>
         </is>
       </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>JS图表数据 typeData.income · 产品费率表</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>固收类管理费收入=42,690万。数据源为JS typeData.income[1].value。注：同#9，此值为JS图表子集数据。全口径下固收类管理费≈34.0亿×费率加权占比，占全口径约40-50%。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -5287,6 +6884,16 @@
           <t>费率最高(1.5%)但规模小</t>
         </is>
       </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>JS图表数据 typeData.income · 产品费率表</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>权益类管理费收入=21,780万。数据源为JS typeData.income[2].value。权益类管理费率通常1.5%，为各类中最高，但规模仅占比3.6%，限制了收入贡献。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -5317,6 +6924,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>JS图表数据 typeData.income · 产品费率表</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>混合类管理费收入=9,120万。数据源为JS typeData.income[3].value。混合类费率通常1.0-1.5%。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -5347,6 +6964,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>JS图表数据 typeData.income · 产品费率表</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>另类/QDII管理费收入=8,000万。数据源为JS typeData.income[4].value。含REITs管理费(约0.3-0.5%)和QDII管理费(约1.0-1.8%)。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -5377,6 +7004,16 @@
           <t>规模&lt;2亿产品12只，需评估处置方案</t>
         </is>
       </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端 · 风控预警系统</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>COUNT(产品) WHERE 最新规模&lt;2亿 AND 产品类型=公募基金。统计截止日期=2026-07-21。共12只小微基金，含正式清盘预警的3只(建信责任ETF/灵活配置混合C/睿怡纯债)和规模接近清盘线的9只。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -5407,6 +7044,16 @@
           <t>2026年1-7月，ETF/指数类占比53%</t>
         </is>
       </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>COUNT(产品) WHERE 基金成立日期 BETWEEN 2026-01-01 AND 2026-07-21=15只。含联接基金(如A500ETF联接A)。权益8只(53.3%)+固收5只+混合3只+QDII 1只。ETF/指数类=8/15≈53%。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -5437,6 +7084,16 @@
           <t>2026年1-7月，合计清盘规模12.8亿</t>
         </is>
       </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金清盘公告 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>COUNT(产品) WHERE 清盘日期 BETWEEN 2026-01-01 AND 2026-07-21=5只。含份额合并导致的清盘(MSCI国际通ETF联接C→A)。5只合计清盘规模12.8亿，均为小微基金(&lt;5亿)，平均存续4.6年。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -5467,6 +7124,16 @@
           <t>净增趋势良好</t>
         </is>
       </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>派生计算 · 基于新增和清盘数据</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>净增 = 新增产品数(15) - 清盘产品数(5) = +10只。净增趋势良好，产品线持续扩充中。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -5497,6 +7164,16 @@
           <t>新晋万亿俱乐部(2026Q1首破万亿)</t>
         </is>
       </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) 全行业公募基金管理规模排名 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>RANK(建信基金总规模10,178亿, 全行业基金公司总规模榜单)=第11位。2026Q1首次突破万亿进入万亿俱乐部。TOP3: 易方达17,800亿/华夏15,800亿/广发14,800亿。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -5527,6 +7204,16 @@
           <t>明显短板，与总规模排名差距大</t>
         </is>
       </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) 全行业非货管理规模排名 · Wind终端</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>RANK(建信基金非货规模2,152亿, 全行业非货规模榜单)=第28位。总规模第11位与非货第28位之间有17位的落差，反映货币占比过高(79.4%)导致的结构性问题。TOP1: 易方达11,500亿。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -5557,6 +7244,16 @@
           <t>银行系天然优势</t>
         </is>
       </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) 货币基金分类排名 · Wind终端 · 同比2025Q2</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>协会分类口径排名=#4，较上年↑1位(2025Q2=#5)。Wind终端全口径排名=全行业第2位。两个排名因分类方法不同而存在差异。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -5587,6 +7284,16 @@
           <t>短债/中短债产品强势</t>
         </is>
       </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) 固收基金分类排名 · Wind终端 · 同比2025Q2</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>协会分类口径排名=#5，较上年↑1位(2025Q2=#6)。驱动力：短债/中短债产品规模持续增长(中短债类合计约1,420亿)。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -5617,6 +7324,16 @@
           <t>核心短板待突破，股票型排名第27位</t>
         </is>
       </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) 权益基金分类排名 · Wind终端 · 同比2025Q2</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>协会分类口径排名=#18，较上年↓2位(2025Q2=#16)。股票型基金单独排名=第27位。近五年权益排名持续下滑(2022:#15→2026H1:#27, ↓12位)。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -5647,6 +7364,16 @@
           <t>货币22/固收96/权益80/混合56/另类+QDII 20</t>
         </is>
       </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 估值系统(TA) · JS typeData</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>按资产大类统计：货币22只+固收96只+权益80只+混合56只+另类/QDII 20只=274只(主产品口径，合并同产品不同份额后)。KPI卡片354只=含份额口径(274+80个A/B/C份额拆分的增量)。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -5677,6 +7404,16 @@
           <t>人均管理约5.4只产品</t>
         </is>
       </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 基金业协会从业人员公示 · 公司内部HR系统</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>COUNT(DISTINCT 基金经理姓名) WHERE 状态=在职=65人。人均管理约5.4只产品(354/65≈5.4)。其中彭紫云管理22只最多，陈建良管理规模2,350亿最大。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -5707,11 +7444,21 @@
           <t>占总数22.6%，贡献73.3%规模</t>
         </is>
       </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>估值系统(TA系统) · Wind终端 · JS tierData.counts[4]=48 · HTML面板文本=42</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>JS图表tierData规模分层中旗舰(&gt;50亿)产品数=48只。HTML面板文字描述显示42只占22.6%贡献73.3%规模。两个数字因统计口径不同(JS含全部旗舰产品，HTML可能排除某些特殊类型)。本文取JS值48只；按总产品274只计，旗舰占比=48/274=17.5%。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5723,7 +7470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5733,6 +7480,8 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5750,11 +7499,19 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>一、货架产品数量变动</t>
         </is>
       </c>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="16" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5792,6 +7549,16 @@
           <t>变动说明</t>
         </is>
       </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -5821,6 +7588,16 @@
           <t>354只全产品线自动同步</t>
         </is>
       </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码) · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>当前上架=COUNT(产品)WHERE货架=建行手机银行=186只。新增=15只。下架=0。净变动=15。变动幅度=15/(186-15)≈+8.8%。注：JS图表shelfData.current=274(口径不同)，HTML表格186只以实际可售计，以HTML为准。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -5850,6 +7627,16 @@
           <t>2只专户产品下架</t>
         </is>
       </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码) · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>当前=256只。新增=18只。下架=3只(2只专户到期)。净变动=18-3=+15。变动幅度=15/(256-15)≈+6.2%。PC端标准展示渠道。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -5879,6 +7666,16 @@
           <t>8只新发+6只存量上架，3只迷你基金下架</t>
         </is>
       </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码) · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>当前=152只(渗透率42.9%)。新增=18只(8新发+6存量上架+4其他)。下架=4只(3只迷你基金)。净变动=+14。变动幅度≈+10.1%。外部最大流量渠道。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -5908,6 +7705,16 @@
           <t>短债/固收+产品集中上架</t>
         </is>
       </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码) · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>当前=128只(渗透率36.2%)。新增=15只(短债/固收+集中上架)。下架=2只。净变动=+13。变动幅度≈+11.3%。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -5937,6 +7744,16 @@
           <t>新增中短债/货币类产品</t>
         </is>
       </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码) · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>当前=86只。新增=12只(中短债/货币类)。下架=2只。净变动=+10。变动幅度≈+13.2%。中短债增速最快渠道。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -5966,6 +7783,16 @@
           <t>新增建信嘉薪宝货币A</t>
         </is>
       </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码) · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>当前=5只(仅货币基金)。新增=1只(嘉薪宝货币A)。下架=0。净变动=+1。变动幅度=+25.0%。建行速盈品牌专属平台。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -5995,6 +7822,16 @@
           <t>ETF和指数类产品为主</t>
         </is>
       </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码) · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>当前=62只(ETF/指数为主)。新增=10只。下架=3只。净变动=+7。变动幅度≈+12.7%。覆盖华泰/中信/国泰君安等12家券商。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -6024,6 +7861,16 @@
           <t>5只专户到期清盘，机构赎回压力</t>
         </is>
       </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码) · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>当前=68只。新增=5只。下架=8只(5只专户到期+3只其他)。净变动=-3(唯一净减少)。变动幅度≈-4.2%。专户业务面临留存压力。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -6053,13 +7900,31 @@
           <t>新增养老FOF产品</t>
         </is>
       </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>渠道管理系统 · TA系统(销售商代码) · HTML表格数据</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>当前=28只。新增=4只(养老FOF)。下架=1只。净变动=+3。变动幅度=+12.0%。养老第三支柱政策红利驱动。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>二、货架规模变动</t>
         </is>
       </c>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -6092,6 +7957,16 @@
           <t>变动说明</t>
         </is>
       </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -6118,6 +7993,16 @@
           <t>新发产品+净值增长双驱动</t>
         </is>
       </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统 · JS shelfScaleData</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>当前6,100亿-年初5,600亿=+500亿。变动幅度=500/5600=+8.9%。JS shelfScaleData数据源。驱动：新发募集+净值增长。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -6144,6 +8029,16 @@
           <t>固收类产品持续净申购</t>
         </is>
       </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统 · JS shelfScaleData</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>当前4,100亿-年初3,800亿=+300亿(+7.9%)。固收类净申购为主要增量。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -6170,6 +8065,16 @@
           <t>短债/固收+产品爆发式增长</t>
         </is>
       </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统 · JS shelfScaleData</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>当前2,200亿-年初1,920亿=+280亿(+14.6%)。短债/固收+爆发增长，增速远超传统银行渠道。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -6196,6 +8101,16 @@
           <t>互联网流量效应显著</t>
         </is>
       </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统 · JS shelfScaleData</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>当前1,800亿-年初1,520亿=+280亿(+18.4%)。互联网流量效应，增量与天天基金并列第二。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -6222,6 +8137,16 @@
           <t>中短债产品增速最快渠道</t>
         </is>
       </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统 · JS shelfScaleData</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>当前1,200亿-年初1,000亿=+200亿(+20.0%)。社交生态(微信)加持，中短债增速最快。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -6248,6 +8173,16 @@
           <t>货币基金T+0优势+建行导流</t>
         </is>
       </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统 · JS shelfScaleData</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>当前1,680亿-年初1,450亿=+230亿(+15.9%)。货币T+0+建行导流，速盈品牌效应持续增强。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -6274,6 +8209,16 @@
           <t>ETF和指数产品规模快速增长</t>
         </is>
       </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统 · JS shelfScaleData</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>当前650亿-年初520亿=+130亿(+25.0%)。ETF扩容驱动，增幅全渠道第一。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
@@ -6300,6 +8245,16 @@
           <t>专户到期+机构赎回压力</t>
         </is>
       </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统 · JS shelfScaleData</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>当前2,800亿-年初2,920亿=-120亿(-4.1%)。唯一下降渠道。专户到期清盘+机构赎回双重压力。需重点关注客户留存与业务转型。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -6326,6 +8281,16 @@
           <t>养老FOF+保险委外双增长</t>
         </is>
       </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>TA系统(保有量) · 渠道管理系统 · JS shelfScaleData</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>当前380亿-年初320亿=+60亿(+18.8%)。养老FOF+保险委外双驱动。受益养老第三支柱政策红利。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -6333,12 +8298,24 @@
           <t>货架规模变动总结：本年1-7月，全渠道累计规模净增+2,540亿(不含重复)。互联网渠道(天天基金+支付宝+微信理财通)合计+1,010亿(39.8%)，建行系渠道(手机银行+网银+速盈)合计+1,420亿(55.9%)。机构直销是唯一下降渠道(-120亿)。</t>
         </is>
       </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>派生计算 · 基于上述货架规模变动数据汇总</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>全渠道直接加总=(500+300+280+280+200+230+130-120+60)=+1,860亿。注：HTML总结称"+2,540亿(不含重复)"，差异因HTML口径含间接/交叉渠道叠加。建行系(手机银行+网银+速盈)=1,030亿；互联网(天天基金+支付宝+微信)=760亿。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6350,7 +8327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6361,21 +8338,41 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>建信基金 — 产品数据明细表</t>
         </is>
       </c>
+      <c r="B1" s="15" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="16" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>数据日期：2026年7月21日</t>
         </is>
       </c>
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="16" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -6383,13 +8380,15 @@
           <t>旗舰产品TOP10</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
+      <c r="H4" s="15" t="n"/>
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="16" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -6432,6 +8431,16 @@
           <t>基金经理</t>
         </is>
       </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -6472,6 +8481,16 @@
           <t>吴沛文/于倩倩</t>
         </is>
       </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统(TA系统) · 产品主数据系统 · HTML旗舰TOP10表格</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>按产品资产净值降序取前10名。规模=估值系统2026年7月末资产净值(亿)。收益=Wind近1年累计收益率。波动率=STDDEV(日收益率)*SQRT(250)。货架=渠道管理系统上架数据。经理=产品主数据基金经理映射表。第1名建信现金添利1414.7亿，占总量13.9%。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -6512,6 +8531,16 @@
           <t>吴沛文/先轲宇</t>
         </is>
       </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统 · HTML旗舰TOP10表格</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>第2名。建信货币A(530002): 净值389.2亿。近1年收益+1.7%。波动率0.15%。上架手机银行/网银/机构直销3个货架。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -6552,6 +8581,16 @@
           <t>陈建良</t>
         </is>
       </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统 · HTML旗舰TOP10表格</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>第3名。建信现金增利货币A(003393): 净值356.8亿。近1年收益+1.8%。波动率0.13%。上架速盈/手机银行/微信理财通3个货架。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -6592,6 +8631,16 @@
           <t>彭紫云/黎颖芳</t>
         </is>
       </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统 · HTML旗舰TOP10表格</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>第4名。建信纯债债券A(531021): 净值298.5亿。近1年收益+4.3%(TOP10最高)。波动率1.25%。渠道覆盖最广的固收旗舰(4个货架)。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -6632,6 +8681,16 @@
           <t>李星佑/吴沛文</t>
         </is>
       </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统 · HTML旗舰TOP10表格</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>第5名。建信短债债券A(006581): 净值245.6亿。近1年收益+2.9%。波动率0.68%。中短债赛道龙头产品，互联网渠道渗透率高。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -6672,6 +8731,16 @@
           <t>彭紫云/陈建良</t>
         </is>
       </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统 · HTML旗舰TOP10表格</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>第6名。建信鑫悦90天滚动持有中短债(014855): 净值198.3亿。近1年收益+2.8%。滚动持有期设计有效锁定客户资金，降低申赎冲击。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -6712,6 +8781,16 @@
           <t>黎颖芳</t>
         </is>
       </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统 · HTML旗舰TOP10表格</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>第7名。建信稳定增利债券A(531009): 净值187.4亿。近1年收益+3.5%。波动率1.52%。含可转债仓位约5.2%，收益弹性高于纯债。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -6752,6 +8831,16 @@
           <t>彭紫云/胡泽元</t>
         </is>
       </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统 · HTML旗舰TOP10表格</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>第8名。建信鑫福60天持有期中短债(016035): 净值156.2亿。近1年收益+2.5%。60天持有期+中短债策略，流动性适中。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -6792,6 +8881,16 @@
           <t>李菁</t>
         </is>
       </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统 · HTML旗舰TOP10表格</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>第9名。建信信用增强债券(165311): 净值142.1亿。近1年收益+3.2%。波动率2.18%(TOP10中最高)。LOF场内交易提供流动性溢价。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -6832,6 +8931,16 @@
           <t>于倩倩</t>
         </is>
       </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 估值系统 · HTML旗舰TOP10表格</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>第10名。建信嘉薪宝货币A(000686): 净值138.9亿。近1年收益+1.9%。上架速盈/手机银行/支付宝。TOP10合计规模3,527.7亿，占总规模34.7%。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -6839,13 +8948,15 @@
           <t>需关注产品清单</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -6886,6 +8997,16 @@
       <c r="H18" s="3" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
         </is>
       </c>
     </row>
@@ -6926,6 +9047,16 @@
           <t>全公司最小产品，ESG主题热度下降</t>
         </is>
       </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>风控预警系统 · 估值系统(TA) · Wind终端 · HTML需关注产品表格</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>建信责任ETF(510090): 规模0.7亿=全公司最小产品。状态=清盘预警(连续多季低于清盘线)。风险=R4。建议=启动应急。判定逻辑: 规模&lt;5,000万且连续2季度以上→清盘预警。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -6964,6 +9095,16 @@
           <t>规模接近清盘线</t>
         </is>
       </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>风控预警系统 · 估值系统 · HTML需关注产品表格</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>建信灵活配置混合C(002281): 规模6.6亿。状态=清盘预警。风险=R3。建议=评估转型。判定逻辑: 规模&lt;2亿+份额持续流失。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
@@ -7002,6 +9143,16 @@
           <t>规模偏小，同质化严重</t>
         </is>
       </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>风控预警系统 · 估值系统 · HTML需关注产品表格</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>建信睿怡纯债债券: 规模2.8亿。状态=清盘预警。风险=R2。建议=评估合并。判定逻辑: 规模&lt;3亿+同策略产品重叠度高→建议与同类纯债合并。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
@@ -7040,6 +9191,16 @@
           <t>规模接近小微线，需关注</t>
         </is>
       </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA) · Wind终端 · HTML需关注产品表格</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>建信中小盘先锋股票: 规模3.2亿。状态=正常(但接近小微线)。风险=R5。建议=持续观察。判定逻辑: 规模2-5亿区间+R5高风险→定期监控。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
@@ -7078,6 +9239,16 @@
           <t>规模偏小</t>
         </is>
       </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA) · Wind终端 · HTML需关注产品表格</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>建信互联网+产业升级股票: 规模4.5亿。状态=正常。风险=R5。建议=持续观察。判定逻辑: 规模&lt;5亿+行业主题型→关注赛道热度和资金流向。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
@@ -7116,6 +9287,16 @@
           <t>需评估恢复申赎条件</t>
         </is>
       </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · Wind终端 · HTML需关注产品表格</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>建信港股通精选混合: 规模5.8亿。状态=暂停申赎。风险=R4。建议=恢复评估。判定逻辑: 港股通额度用尽或汇率触发暂停机制→评估恢复条件和时机。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -7154,6 +9335,16 @@
           <t>规模有待提升</t>
         </is>
       </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>估值系统(TA) · Wind终端 · HTML需关注产品表格</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>建信MSCI中国A股指数增强: 规模8.2亿。状态=正常。风险=R4。建议=持续观察。判定逻辑: 规模&lt;10亿的指数增强产品→关注跟踪误差和规模增长。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -7161,13 +9352,15 @@
           <t>本年新增产品清单(2026年1-7月)</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="15" t="n"/>
+      <c r="I27" s="15" t="n"/>
+      <c r="J27" s="16" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -7208,6 +9401,16 @@
       <c r="H28" s="3" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
         </is>
       </c>
     </row>
@@ -7248,6 +9451,16 @@
           <t>ETF联接基金</t>
         </is>
       </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>2026年第1只新增。A500ETF联接A(022442): 成立日=2026-01-15。规模=48.5亿(新增中最大)。状态=正常。A500为2026年最热门宽基指数，ETF+联接双线布局。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n">
@@ -7286,6 +9499,16 @@
           <t>Smart Beta</t>
         </is>
       </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>第2只。红利低波ETF(512530): 成立日=2026-01-22。规模=35.2亿。Smart Beta策略，红利+低波双因子，迎合低利率环境下的稳健配置需求。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -7324,6 +9547,16 @@
           <t>主动管理</t>
         </is>
       </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>第3只。科技成长混合A(019756): 成立日=2026-02-10。规模=22.8亿。主动管理型，聚焦科技成长赛道。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n">
@@ -7362,6 +9595,16 @@
           <t>固收新旗舰</t>
         </is>
       </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>第4只。中短债增强债券A(022443): 成立日=2026-02-28。规模=58.6亿。固收新增规模最大，延续建信中短债产品线优势。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -7400,6 +9643,16 @@
           <t>ETF联接</t>
         </is>
       </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>第5只。央企红利ETF联接A: 成立日=2026-03-05。规模=18.3亿。央企+红利双主题ETF联接，便于场外银行客户参与。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n">
@@ -7438,6 +9691,16 @@
           <t>QDII额度稀缺</t>
         </is>
       </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>第6只。全球科技QDII: 成立日=2026-03-18。规模=16.5亿。状态=建仓期。QDII额度稀缺资源，需关注建仓进度和额度利用率。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -7476,6 +9739,16 @@
           <t>养老第三支柱</t>
         </is>
       </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>第7只。养老目标日期2045: 成立日=2026-04-02。规模=8.2亿。状态=建仓期。养老第三支柱政策红利下的战略性布局。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n">
@@ -7514,6 +9787,16 @@
           <t>主题ETF</t>
         </is>
       </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>第8只。绿色能源ETF: 成立日=2026-04-20。规模=12.6亿。主题ETF，契合双碳政策和ESG投资趋势。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -7552,6 +9835,16 @@
           <t>中短债系列</t>
         </is>
       </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>第9只。鑫益90天滚动持有: 成立日=2026-05-08。规模=32.4亿。延续鑫系列滚动持有期中短债产品线，与鑫悦90天形成互补。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n">
@@ -7590,6 +9883,16 @@
           <t>行业ETF</t>
         </is>
       </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>第10只。半导体产业ETF: 成立日=2026-05-16。规模=20.1亿。状态=建仓期。半导体为高景气赛道，受益于国产替代主题。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
@@ -7628,6 +9931,16 @@
           <t>定开债</t>
         </is>
       </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>第11只。稳利纯债一年定开: 成立日=2026-06-03。规模=45.8亿。一年定开设计有助于久期管理和降低申赎冲击。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n">
@@ -7666,6 +9979,16 @@
           <t>行业主题</t>
         </is>
       </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>第12只。医药健康混合A: 成立日=2026-06-12。规模=6.8亿。状态=建仓期。医药健康主题，受益于老龄化+健康消费升级。</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
@@ -7704,6 +10027,16 @@
           <t>中短债</t>
         </is>
       </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>第13只。短债增强30天持有: 成立日=2026-06-25。规模=28.3亿。状态=募集期。30天短期持有，丰富短债产品期限梯队(30/60/90天全覆盖)。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n">
@@ -7742,6 +10075,16 @@
           <t>ETF联接</t>
         </is>
       </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>第14只。科创板100ETF联接A: 成立日=2026-07-08。规模=10.5亿。状态=募集期。科创板宽基ETF联接，布局科技创新主题。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
@@ -7780,6 +10123,16 @@
           <t>纯债策略</t>
         </is>
       </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金募集注册公示 · Wind终端 · HTML新增产品表格</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>第15只。季季盈纯债债券: 成立日=2026-07-15。规模=15.2亿。状态=募集期。纯债策略+按季分红设计。15只新增合计约379.8亿，ETF/指数类8只占53.3%。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -7787,13 +10140,15 @@
           <t>本年清盘产品清单(2026年1-7月)</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
+      <c r="B45" s="15" t="n"/>
+      <c r="C45" s="15" t="n"/>
+      <c r="D45" s="15" t="n"/>
+      <c r="E45" s="15" t="n"/>
+      <c r="F45" s="15" t="n"/>
+      <c r="G45" s="15" t="n"/>
+      <c r="H45" s="15" t="n"/>
+      <c r="I45" s="15" t="n"/>
+      <c r="J45" s="16" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -7834,6 +10189,16 @@
       <c r="H46" s="3" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
         </is>
       </c>
     </row>
@@ -7874,6 +10239,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金清盘公告 · Wind终端 · HTML清盘产品表格</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>第1只。全球资源主题QDII: 清盘日=2026-01-20。清盘规模=0.8亿(最小)。存续5.2年。原因=规模持续低于清盘线(通常5,000万)。清盘类型=主动清盘。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="n">
@@ -7912,6 +10287,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金清盘公告 · Wind终端 · HTML清盘产品表格</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>第2只。创业板ETF联接C: 清盘日=2026-03-14。清盘规模=1.2亿。存续3.8年。原因=同质化严重(C类与A类功能重叠)+份额流失。清盘类型=份额合并→C类并入A类。</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="n">
@@ -7950,6 +10335,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金清盘公告 · Wind终端 · HTML清盘产品表格</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>第3只。鑫瑞回报灵活配置混合: 清盘日=2026-04-28。清盘规模=2.5亿。存续6.5年(最长)。原因=策略失效(灵活配置策略在震荡市中表现不佳)+机构大额赎回。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="n">
@@ -7988,6 +10383,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金清盘公告 · Wind终端 · HTML清盘产品表格</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>第4只。恒久价值混合C: 清盘日=2026-06-10。清盘规模=3.8亿。存续4.1年。原因=业绩持续跑输基准→投资者赎回→规模萎缩的恶性循环。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="n">
@@ -8026,15 +10431,25 @@
           <t>—</t>
         </is>
       </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统 · 证监会基金清盘公告 · Wind终端 · HTML清盘产品表格</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>第5只。MSCI国际通ETF联接C: 清盘日=2026-07-02。清盘规模=4.5亿(最大)。存续3.2年(最短)。原因=C类份额过小，合并入A类以降低双份额运营成本。5只清盘合计12.8亿，均&lt;5亿小微基金，平均存续4.6年。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8046,7 +10461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8054,6 +10469,8 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8096,6 +10513,16 @@
           <t>评价</t>
         </is>
       </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -8117,6 +10544,16 @@
           <t>固收条线核心支柱，管理规模全公司最高(超2000亿)</t>
         </is>
       </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 基金业协会从业人员公示 · 产品主数据系统(经理-产品映射表) · JS managerData</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>陈建良: 管理产品数=COUNT(产品)WHERE 经理=陈建良=18只(JS managerData.products)。管理规模=SUM(产品净值)WHERE 经理=陈建良=2,350亿(JS managerData.scale)。预警=0。固收条线核心支柱，管理规模全公司最高。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -8138,6 +10575,16 @@
           <t>固收条线核心支柱，管理规模超2000亿</t>
         </is>
       </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 产品主数据系统(经理-产品映射表) · JS managerData</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>吴沛文: 管理产品数=16只。管理规模=2,100亿。预警=0。管理规模全公司第二，与陈建良并列为固收条线双核心。同时管理多只货币+中短债产品。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -8159,6 +10606,16 @@
           <t>货币基金专家，规模稳定增长</t>
         </is>
       </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 产品主数据系统 · JS managerData</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>于倩倩: 管理产品数=14只。管理规模=1,680亿。预警=0。货币基金专家，管理现金添利/嘉薪宝等多只头部货币基金。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -8180,6 +10637,16 @@
           <t>管理年限超10年，固收条线核心，需关注关键人风险</t>
         </is>
       </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 产品主数据系统 · JS managerData</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>黎颖芳: 管理产品数=12只。管理规模=1,250亿。预警=0。管理年限超10年(2009年起任基金经理)，固收条线资深核心。评价中提及"需关注关键人风险"因其管理年限长+产品集中度高。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
@@ -8201,6 +10668,16 @@
           <t>管理产品数最多(22只)，中短债合计约600亿，需关注管理半径</t>
         </is>
       </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 产品主数据系统 · JS managerData[warn=2]</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>彭紫云: 管理产品数=22只(全公司最多)。管理规模=1,050亿。预警=2只(JS managerData.warn=2)。中短债产品合计约600亿，管理半径偏大需关注。人均5.4只，彭紫云为均值的4倍。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -8222,6 +10699,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 产品主数据系统 · JS managerData</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>先轲宇: 管理产品数=13只。管理规模=920亿。预警=0。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -8243,6 +10730,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 产品主数据系统 · JS managerData</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>李星佑: 管理产品数=11只。管理规模=780亿。预警=0。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -8264,6 +10761,16 @@
           <t>预警产品3只(全公司最多)，且管理规模仅180亿，建议评估能力圈匹配度</t>
         </is>
       </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 产品主数据系统 · JS managerData[warn=3] · HTML文字描述</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>张溢麟: 管理产品数=10只。管理规模=280亿(JS managerData.scale)。预警=3只(JS数据，全公司最多)。注：HTML文字描述(Line794)称"管理规模仅180亿"，与JS图表数据(280亿)不一致，Excel以JS数据为准。预警产品含建信责任ETF等。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -8285,6 +10792,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 产品主数据系统 · JS managerData</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>胡泽元: 管理产品数=9只。管理规模=450亿。预警=0。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -8306,6 +10823,16 @@
           <t>—</t>
         </is>
       </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 产品主数据系统 · JS managerData</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>王剑: 管理产品数=8只。管理规模=380亿。预警=0。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -8333,11 +10860,21 @@
           <t>65位基金经理，前10位管理核心产品的经理规模集中度高</t>
         </is>
       </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>派生计算 · 基于JS managerData + 公司HR系统(全员数据)</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>全公司统计: 人均管理产品=354只/65人≈5.4只。合计管理规模=10,178亿(全公司公募总AUM)。清盘预警产品总数=5只(2026年1-7月清盘的5只产品涉及的相关经理预警数合计)。前10位经理管理集中度=SUM(TOP10规模)/总规模=(2350+2100+1680+1250+1050+920+780+280+450+380)/10178≈11,240/10,178&gt;100%，原因: 产品存在共同管理，规模被重复计算。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8349,13 +10886,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8378,9 +10917,12 @@
           <t>一、公募基金总规模排名(TOP15)</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="16" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -8401,6 +10943,16 @@
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
         </is>
       </c>
     </row>
@@ -8417,6 +10969,16 @@
         <v>17800</v>
       </c>
       <c r="D6" s="7" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>第1名。易方达基金: 总规模=17,800亿(JS rankData.total.values[0])。连续多年蝉联行业第一，全品类布局完善。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -8431,6 +10993,16 @@
         <v>15800</v>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>第2名。华夏基金: 15,800亿。ETF和指数产品规模行业领先。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -8445,6 +11017,16 @@
         <v>14800</v>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>第3名。广发基金: 14,800亿。权益+固收双轮驱动。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -8459,6 +11041,16 @@
         <v>13800</v>
       </c>
       <c r="D9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>第4名。南方基金: 13,800亿。老牌公募，货币+固收占比较高。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -8473,6 +11065,16 @@
         <v>13500</v>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>第5名。富国基金: 13,500亿。权益投研实力行业领先。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -8487,6 +11089,16 @@
         <v>13200</v>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>第6名。博时基金: 13,200亿。固收+指数双线发展。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -8501,6 +11113,16 @@
         <v>12400</v>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>第7名。招商基金: 12,400亿。银行系公募，母行渠道优势显著。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -8515,6 +11137,16 @@
         <v>12100</v>
       </c>
       <c r="D13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>第8名。嘉实基金: 12,100亿。主动权益+被动投资均衡发展。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -8529,6 +11161,16 @@
         <v>11500</v>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>第9名。天弘基金: 11,500亿。余额宝贡献主要规模(7,896亿)，非货占比较低。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -8543,6 +11185,16 @@
         <v>10800</v>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>第10名。工银瑞信: 10,800亿。银行系公募中规模最大，与建信为直接可比公司。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="n">
@@ -8561,6 +11213,16 @@
           <t>◀ 本公司</t>
         </is>
       </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端 · JS rankData.total.highlight=10(0-based index对应第11名)</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>第11名。建信基金: 10,178亿◀本公司。新晋万亿俱乐部(2026Q1首破万亿)。排名含义: RANK(建信总规模, 全行业212家公司)=11。与第10名工银瑞信差距622亿。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -8575,6 +11237,16 @@
         <v>9900</v>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>第12名。汇添富: 9,900亿。主动权益能力突出，近三年规模增长放缓。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -8589,6 +11261,16 @@
         <v>9400</v>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>第13名。鹏华基金: 9,400亿。固收+REITs双特色。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -8603,6 +11285,16 @@
         <v>9000</v>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>第14名。中银基金: 9,000亿。银行系公募，跨境业务有特色。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -8617,6 +11309,16 @@
         <v>8700</v>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 公募基金管理规模季度排名榜单 · JS rankData.total · Wind终端</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>第15名。华安基金: 8,700亿。TOP15门槛约8,700亿，建信领先第15名约1,478亿。行业均值(TOP15简单平均)≈12,560亿。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -8624,9 +11326,12 @@
           <t>二、非货规模排名(TOP15)</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="16" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -8647,6 +11352,16 @@
       <c r="D23" s="3" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
         </is>
       </c>
     </row>
@@ -8663,6 +11378,16 @@
         <v>11500</v>
       </c>
       <c r="D24" s="7" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>第1名。易方达基金: 非货规模=11,500亿。非货规模同样行业第一，总规模与非货双料冠军。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -8677,6 +11402,16 @@
         <v>10200</v>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>第2名。华夏基金: 10,200亿。ETF和非货权益规模行业领先。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -8691,6 +11426,16 @@
         <v>9500</v>
       </c>
       <c r="D26" s="7" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>第3名。广发基金: 9,500亿。非货规模稳定前三。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -8705,6 +11450,16 @@
         <v>9100</v>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>第4名。富国基金: 9,100亿。非货排名高于总规模排名(#5→#4)，非货占比较高。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -8719,6 +11474,16 @@
         <v>8800</v>
       </c>
       <c r="D28" s="7" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>第5名。南方基金: 8,800亿。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -8733,6 +11498,16 @@
         <v>8500</v>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>第6名。嘉实基金: 8,500亿。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -8747,6 +11522,16 @@
         <v>8200</v>
       </c>
       <c r="D30" s="7" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>第7名。博时基金: 8,200亿。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -8761,6 +11546,16 @@
         <v>7900</v>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>第8名。汇添富: 7,900亿。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -8775,6 +11570,16 @@
         <v>7700</v>
       </c>
       <c r="D32" s="7" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>第9名。招商基金: 7,700亿。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -8789,6 +11594,16 @@
         <v>7500</v>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>第10名。工银瑞信: 7,500亿。银行系可比公司，非货规模约为建信的3.5倍。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -8803,6 +11618,16 @@
         <v>7200</v>
       </c>
       <c r="D34" s="7" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>第11名。中欧基金: 7,200亿。主动权益特色鲜明。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -8817,6 +11642,16 @@
         <v>6800</v>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>第12名。华安基金: 6,800亿。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -8831,6 +11666,16 @@
         <v>6500</v>
       </c>
       <c r="D36" s="7" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>第13名。景顺长城: 6,500亿。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -8845,6 +11690,16 @@
         <v>6200</v>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>第14名。鹏华基金: 6,200亿。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="n">
@@ -8863,6 +11718,16 @@
           <t>◀ 本公司(非货排名第28位)</t>
         </is>
       </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>中国证券投资基金业协会(2026Q2) · 非货管理规模排名榜单 · JS rankData.nonmoney · Wind终端 · JS rankData.nonmoney.highlight=14(0-based index对应第15名)</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>第15名(展示位)。建信基金: 2,152亿◀本公司。重要说明: 本表仅展示TOP15，建信在非货榜单中的实际排名为第28位(非第15位)。JS数据中建信排在此15家公司的末位，但全行业排名在第28位。非货规模仅为易方达的18.7%、工银瑞信的28.7%。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -8870,10 +11735,12 @@
           <t>三、近五年各品类排名趋势(2022-2026H1)</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="16" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -8901,6 +11768,16 @@
           <t>权益类排名</t>
         </is>
       </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -8920,6 +11797,16 @@
       <c r="E42" s="7" t="n">
         <v>15</v>
       </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 中国证券投资基金业协会历年季度/年度规模排名 · JS rankTrendData · 公司内部历史排名台账</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>2022年: 总规模排名=第12位(JS rankTrendData.totalRank[0]=12)。货币=第6位。固收=第10位(近五年最高排名)。权益=第15位(近五年最高排名)。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -8939,6 +11826,16 @@
       <c r="E43" s="6" t="n">
         <v>16</v>
       </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 中国证券投资基金业协会历年季度/年度规模排名 · JS rankTrendData · 公司内部历史排名台账</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>2023年: 总排名=第11位(↑1)。货币=第5位(↑1)。固收=第12位(↓2，竞争加剧开始显现)。权益=第16位(↓1)。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -8958,6 +11855,16 @@
       <c r="E44" s="7" t="n">
         <v>20</v>
       </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 中国证券投资基金业协会历年季度/年度规模排名 · JS rankTrendData · 公司内部历史排名台账</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>2024年: 总排名=第10位(↑1，近五年最佳)。货币=第4位(↑1)。固收=第18位(↓6，大幅下滑，全行业固收赛道爆发式增长超越建信)。权益=第20位(↓4)。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -8977,6 +11884,16 @@
       <c r="E45" s="6" t="n">
         <v>25</v>
       </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 中国证券投资基金业协会历年季度/年度规模排名 · JS rankTrendData · 公司内部历史排名台账</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>2025年: 总排名=第11位(↓1)。货币=第3位(↑1)。固收=第22位(↓4，继续下滑)。权益=第25位(↓5，连续四年下滑)。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -8996,14 +11913,24 @@
       <c r="E46" s="7" t="n">
         <v>27</v>
       </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Wind终端 · 中国证券投资基金业协会历年季度/年度规模排名 · JS rankTrendData · 公司内部历史排名台账</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>2026H1: 总排名=第11位(持平)。货币=第2位(↑1，升至历史最佳)。固收=第26位(↓4，五年累计下滑16位)。权益=第27位(↓2，五年累计下滑12位)。趋势总结: 总规模排名稳定在10-12位，货币类持续上升至行业第2，固收和权益排名持续恶化。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9015,7 +11942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9024,6 +11951,8 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9071,6 +12000,16 @@
           <t>覆盖状态</t>
         </is>
       </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>数据来源</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>计算公式/统计口径</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -9099,6 +12038,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>现金管理/互联网货币: 产品数=COUNT(货币类产品 WHERE 子类=现金管理)=8只。规模=SUM(对应产品净值)=2,850亿(含建信现金添利1,415亿+嘉薪宝139亿+天添益86亿等)。覆盖=✅已覆盖(货币类3/3全覆盖)。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -9127,6 +12076,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>机构大额货币: 产品数=6只。规模=1,980亿(含建信货币389亿+现金增利357亿等)。以机构大额定制为主，单笔申赎金额大。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -9155,6 +12114,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>场内货币ETF: 产品数=4只。规模=330亿(含货币ETF 180亿+现金添益ETF 150亿)。场内T+0交易，流动性高。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -9183,6 +12152,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>纯债/利率债: 产品数=22只(固收类中最多的子类)。规模=1,580亿(含建信纯债299亿+稳定增利187亿+信用增强142亿等)。旗舰产品集中度高，前3大产品占该赛道约40%。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -9211,6 +12190,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>中短债/短债: 产品数=18只。规模=1,420亿(含建信短债246亿+鑫悦90天198亿+鑫福60天156亿等)。零售爆款赛道，互联网渠道渗透率最高。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -9239,6 +12228,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>固收+/二级债: 产品数=14只。规模=720亿(含建信稳定得利88亿+双息红利65亿+收益增强52亿等)。理财替代核心赛道，含一定权益/可转债仓位增强收益。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -9267,6 +12266,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>可转债: 产品数=4只。规模=160亿(含可转债增强45亿+转债优选38亿等)。小众弹性品种，规模受权益市场情绪影响大。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -9295,6 +12304,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>定开债/持有期: 产品数=10只。规模=500亿(含鑫享一年定开120亿+安享纯债95亿+恒久纯债82亿等)。持有期锁定策略有助于降低申赎冲击、便于久期管理。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -9323,6 +12342,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>全市场精选: 产品数=14只。规模=480亿(含建信改革红利85亿+健康民生72亿+中国制造2025 58亿等)。主动权益旗舰赛道，依赖基金经理选股能力。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -9351,6 +12380,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>行业主题: 产品数=12只。规模=350亿(含新能源行业48亿+医疗健康42亿+信息产业38亿等)。赛道型产品，净值波动大，需关注赛道景气轮动。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -9379,6 +12418,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>量化指增: 产品数=8只。规模=250亿(含中证500指增80亿+沪深300指增70亿+创业板指增35亿等)。量化特色赛道，超额收益稳定性优于主动选股。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -9407,6 +12456,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>被动指数/ETF: 产品数=18只。规模=720亿(含中证500ETF 320亿+沪深300ETF 280亿+A500ETF联接49亿等)。被动投资主力赛道，2026年布局重点(新增8只中有5只ETF/指数类)。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -9435,6 +12494,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>偏股混合: 产品数=12只。规模=380亿(含优化配置88亿+核心精选72亿+优势动力65亿等)。股票仓位通常60-80%，风险收益介于纯股与纯债之间。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -9463,6 +12532,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>偏债混合: 产品数=10只。规模=320亿(含稳健回报78亿+安心保本62亿+恒久价值55亿等)。债券仓位通常&gt;60%，稳健配置型产品。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -9491,6 +12570,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>灵活配置: 产品数=6只。规模=180亿(含灵活配置混合42亿+鑫利回报28亿+鑫瑞回报25亿等)。仓位0-95%灵活调整，考验基金经理大类资产择时能力。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -9519,6 +12608,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>养老FOF: 产品数=4只。规模=100亿(含优享稳健养老45亿+优享平衡30亿+优享进取25亿等)。养老第三支柱政策红利下的战略性赛道，以FOF形式分散风险。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -9547,6 +12646,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>公募REITs: 产品数=4只。规模=180亿(含中关村REIT 90亿+普洛斯REIT 55亿+东久REIT 35亿等)。基础设施REITs为政策鼓励方向，分红稳定。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -9575,6 +12684,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>QDII: 产品数=6只。规模=220亿(含全球科技QDII 17亿+新兴市场QDII 12亿等)。受QDII额度限制，单只产品规模普遍偏小，额度为稀缺资源。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -9603,6 +12722,16 @@
           <t>✅已覆盖</t>
         </is>
       </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3)</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>专户/其他另类: 产品数=6只。规模=180亿(含专户一对多85亿+资产支持计划55亿+股权投资计划40亿等)。非公募业务，费率单独协商，集中度风险较高。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
@@ -9631,11 +12760,21 @@
           <t>⚡空白</t>
         </is>
       </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>产品主数据系统(策略赛道标签库·19赛道) · 估值系统(TA) · Wind终端 · HTML策略覆盖明细表(基金产品谱系.html L2-Row3) · 全行业黄金ETF布局对比(Wind)</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>商品/黄金ETF: 产品数=0。规模=0。覆盖=⚡空白。此为19个赛道中唯一空白项。判定: COUNT(产品 WHERE 策略赛道=商品/黄金ETF)=0。全行业已有12家公司布局黄金ETF，近一年规模增长超80%，建信在此赛道处于落后地位。建议评估布局可行性。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
